--- a/main/ig/FRFamilyMemberHistoryLMCDAFHIR.xlsx
+++ b/main/ig/FRFamilyMemberHistoryLMCDAFHIR.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="63">
   <si>
     <t>Property</t>
   </si>
@@ -40,7 +40,7 @@
     <t>Title</t>
   </si>
   <si>
-    <t>Mapping Métier/CDA/FHIR : "Antécédent familial observé"</t>
+    <t>Mapping Métier/CDA/FHIR : "Antécédent familial"</t>
   </si>
   <si>
     <t>Status</t>
@@ -55,7 +55,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-16T15:39:37+00:00</t>
+    <t>2026-08-05T12:15:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -79,7 +79,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Mapping des éléments du modèle métier FRLMAntecedentFamilialObserve vers le profil CDA FRCDAAntecedentFamilialObserve, puis vers le profil FHIR FRFamilyMemberHistoryDocument.</t>
+    <t>Mapping des éléments du modèle métier FRLMFamilyMemberHistory vers le profil CDA FRCDAAntecedentsFamiliaux, puis vers le profil FHIR FRFamilyMemberHistoryDocument.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -100,118 +100,109 @@
     <t>Target</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-antecedent-familial-observe</t>
+    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-family-member-history</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-cda-antecedent-familial-observe</t>
-  </si>
-  <si>
-    <t>FRLMAntecedentFamilialObserve</t>
+    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-cda-antecedents-familiaux</t>
+  </si>
+  <si>
+    <t>FRLMFamilyMemberHistory</t>
   </si>
   <si>
     <t>equivalent</t>
   </si>
   <si>
-    <t>FRCDAAntecedentFamilialObserve</t>
-  </si>
-  <si>
-    <t>FRLMAntecedentFamilialObserve.identifiant</t>
-  </si>
-  <si>
-    <t>FRCDAAntecedentFamilialObserve.id</t>
-  </si>
-  <si>
-    <t>FRLMAntecedentFamilialObserve.statut</t>
-  </si>
-  <si>
-    <t>FRCDAAntecedentFamilialObserve.statusCode</t>
-  </si>
-  <si>
-    <t>FRLMAntecedentFamilialObserve.code</t>
-  </si>
-  <si>
-    <t>FRCDAAntecedentFamilialObserve.code</t>
-  </si>
-  <si>
-    <t>FRLMAntecedentFamilialObserve.descriptionNarrative</t>
-  </si>
-  <si>
-    <t>FRCDAAntecedentFamilialObserve.text</t>
-  </si>
-  <si>
-    <t>FRLMAntecedentFamilialObserve.horodatage</t>
-  </si>
-  <si>
-    <t>FRCDAAntecedentFamilialObserve.effectiveTime</t>
-  </si>
-  <si>
-    <t>FRLMAntecedentFamilialObserve.resultat</t>
-  </si>
-  <si>
-    <t>FRCDAAntecedentFamilialObserve.value</t>
-  </si>
-  <si>
-    <t>FRLMAntecedentFamilialObserve.interpretation</t>
-  </si>
-  <si>
-    <t>FRCDAAntecedentFamilialObserve.interpretationCode</t>
-  </si>
-  <si>
-    <t>FRLMAntecedentFamilialObserve.methode</t>
-  </si>
-  <si>
-    <t>FRCDAAntecedentFamilialObserve.methodCode</t>
-  </si>
-  <si>
-    <t>FRLMAntecedentFamilialObserve.site</t>
-  </si>
-  <si>
-    <t>FRCDAAntecedentFamilialObserve.targetSiteCode</t>
-  </si>
-  <si>
-    <t>FRLMAntecedentFamilialObserve.auteur</t>
-  </si>
-  <si>
-    <t>FRCDAAntecedentFamilialObserve.author</t>
+    <t>FRCDAAntecedentsFamiliaux</t>
+  </si>
+  <si>
+    <t>FRLMFamilyMemberHistory.header.status</t>
+  </si>
+  <si>
+    <t>FRCDAAntecedentsFamiliaux.statusCode</t>
+  </si>
+  <si>
+    <t>FRLMFamilyMemberHistory.relatedPerson</t>
+  </si>
+  <si>
+    <t>FRCDAAntecedentsFamiliaux.subject.relatedSubject</t>
+  </si>
+  <si>
+    <t>FRLMFamilyMemberHistory.condition</t>
+  </si>
+  <si>
+    <t>FRCDAAntecedentsFamiliaux.component:frAntecedentFamilialObserve</t>
+  </si>
+  <si>
+    <t>FRLMFamilyMemberHistory.condition.code</t>
+  </si>
+  <si>
+    <t>FRCDAAntecedentsFamiliaux.component:frAntecedentFamilialObserve.code</t>
+  </si>
+  <si>
+    <t>FRLMFamilyMemberHistory.condition.outcome</t>
+  </si>
+  <si>
+    <t>FRCDAAntecedentsFamiliaux.component:frAntecedentFamilialObserve.value</t>
+  </si>
+  <si>
+    <t>FRLMFamilyMemberHistory.condition.contributedToDeath</t>
+  </si>
+  <si>
+    <t>related-to</t>
+  </si>
+  <si>
+    <t>FRLMFamilyMemberHistory.condition.onset[x]</t>
+  </si>
+  <si>
+    <t>FRCDAAntecedentsFamiliaux.component:frAntecedentFamilialObserve.effectiveTime</t>
+  </si>
+  <si>
+    <t>FRLMFamilyMemberHistory.condition.bodySite</t>
+  </si>
+  <si>
+    <t>FRCDAAntecedentsFamiliaux.component:frAntecedentFamilialObserve.targetSiteCode</t>
+  </si>
+  <si>
+    <t>FRLMFamilyMemberHistory.note</t>
+  </si>
+  <si>
+    <t>FRCDAAntecedentsFamiliaux.text</t>
   </si>
   <si>
     <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-family-member-history-document</t>
   </si>
   <si>
+    <t>FRFamilyMemberHistoryDocument</t>
+  </si>
+  <si>
+    <t>FRFamilyMemberHistoryDocument.status</t>
+  </si>
+  <si>
+    <t>FRFamilyMemberHistoryDocument.relationship</t>
+  </si>
+  <si>
     <t>FRFamilyMemberHistoryDocument.condition</t>
   </si>
   <si>
-    <t>FRFamilyMemberHistoryDocument.identifier</t>
-  </si>
-  <si>
-    <t>FRFamilyMemberHistoryDocument.status</t>
+    <t>FRFamilyMemberHistoryDocument.condition.code</t>
+  </si>
+  <si>
+    <t>FRFamilyMemberHistoryDocument.condition.outcome</t>
+  </si>
+  <si>
+    <t>FRFamilyMemberHistoryDocument.condition.contributedToDeath</t>
   </si>
   <si>
     <t>FRFamilyMemberHistoryDocument.condition.onset[x]</t>
   </si>
   <si>
-    <t>FRFamilyMemberHistoryDocument.condition.code</t>
-  </si>
-  <si>
-    <t>FRFamilyMemberHistoryDocument.condition.note</t>
-  </si>
-  <si>
-    <t>FRFamilyMemberHistoryDocument.condition.outcome</t>
-  </si>
-  <si>
-    <t>FRFamilyMemberHistoryDocument.condition.extension:FRInterpretationExtension</t>
-  </si>
-  <si>
-    <t>FRFamilyMemberHistoryDocument.condition.extension:FRMethodExtension</t>
-  </si>
-  <si>
     <t>FRFamilyMemberHistoryDocument.condition.extension:FRFamilyMemberHistoryBodySiteExtension</t>
   </si>
   <si>
-    <t>FRFamilyMemberHistoryDocument.condition.extension:FRActorExtension</t>
+    <t>FRFamilyMemberHistoryDocument.note</t>
   </si>
 </sst>
 </file>
@@ -463,7 +454,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -584,10 +575,10 @@
       </c>
       <c r="B9" s="2"/>
       <c r="C9" t="s" s="2">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="D9" t="s" s="2">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E9" s="2"/>
     </row>
@@ -623,25 +614,12 @@
       </c>
       <c r="B12" s="2"/>
       <c r="C12" t="s" s="2">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="D12" t="s" s="2">
         <v>51</v>
       </c>
       <c r="E12" s="2"/>
-    </row>
-    <row r="13">
-      <c r="A13" t="s" s="2">
-        <v>52</v>
-      </c>
-      <c r="B13" s="2"/>
-      <c r="C13" t="s" s="2">
-        <v>32</v>
-      </c>
-      <c r="D13" t="s" s="2">
-        <v>53</v>
-      </c>
-      <c r="E13" s="2"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
@@ -650,7 +628,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -672,7 +650,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B2" t="s" s="2">
         <v>29</v>
@@ -681,7 +659,7 @@
         <v>29</v>
       </c>
       <c r="D2" t="s" s="2">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E2" t="s" s="2">
         <v>29</v>
@@ -689,146 +667,133 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D3" t="s" s="2">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="E3" s="2"/>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D4" t="s" s="2">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E4" s="2"/>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" t="s" s="2">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="D5" t="s" s="2">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E5" s="2"/>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D6" t="s" s="2">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E6" s="2"/>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D7" t="s" s="2">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E7" s="2"/>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D8" t="s" s="2">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E8" s="2"/>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B9" s="2"/>
       <c r="C9" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D9" t="s" s="2">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E9" s="2"/>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B10" s="2"/>
       <c r="C10" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D10" t="s" s="2">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E10" s="2"/>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B11" s="2"/>
       <c r="C11" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D11" t="s" s="2">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E11" s="2"/>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B12" s="2"/>
       <c r="C12" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D12" t="s" s="2">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E12" s="2"/>
-    </row>
-    <row r="13">
-      <c r="A13" t="s" s="2">
-        <v>53</v>
-      </c>
-      <c r="B13" s="2"/>
-      <c r="C13" t="s" s="2">
-        <v>32</v>
-      </c>
-      <c r="D13" t="s" s="2">
-        <v>65</v>
-      </c>
-      <c r="E13" s="2"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>

--- a/main/ig/FRFamilyMemberHistoryLMCDAFHIR.xlsx
+++ b/main/ig/FRFamilyMemberHistoryLMCDAFHIR.xlsx
@@ -55,7 +55,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-05T12:15:23+00:00</t>
+    <t>2026-08-11T08:03:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/FRFamilyMemberHistoryLMCDAFHIR.xlsx
+++ b/main/ig/FRFamilyMemberHistoryLMCDAFHIR.xlsx
@@ -55,7 +55,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-11T08:03:55+00:00</t>
+    <t>2026-08-11T09:29:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/FRFamilyMemberHistoryLMCDAFHIR.xlsx
+++ b/main/ig/FRFamilyMemberHistoryLMCDAFHIR.xlsx
@@ -55,7 +55,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-11T09:29:09+00:00</t>
+    <t>2026-08-13T09:45:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/FRFamilyMemberHistoryLMCDAFHIR.xlsx
+++ b/main/ig/FRFamilyMemberHistoryLMCDAFHIR.xlsx
@@ -55,7 +55,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-13T09:45:33+00:00</t>
+    <t>2026-08-13T14:36:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/FRFamilyMemberHistoryLMCDAFHIR.xlsx
+++ b/main/ig/FRFamilyMemberHistoryLMCDAFHIR.xlsx
@@ -55,7 +55,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-13T14:36:19+00:00</t>
+    <t>2026-08-14T12:00:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/FRFamilyMemberHistoryLMCDAFHIR.xlsx
+++ b/main/ig/FRFamilyMemberHistoryLMCDAFHIR.xlsx
@@ -55,7 +55,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-14T12:00:06+00:00</t>
+    <t>2026-08-14T14:57:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/FRFamilyMemberHistoryLMCDAFHIR.xlsx
+++ b/main/ig/FRFamilyMemberHistoryLMCDAFHIR.xlsx
@@ -55,7 +55,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-14T14:57:39+00:00</t>
+    <t>2026-08-20T08:45:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -100,13 +100,13 @@
     <t>Target</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-family-member-history</t>
+    <t>https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/fr-lm-family-member-history|0.1.0</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-cda-antecedents-familiaux</t>
+    <t>https://interop.esante.gouv.fr/ig/cda/document-core/StructureDefinition/fr-cda-antecedents-familiaux|0.1.0</t>
   </si>
   <si>
     <t>FRLMFamilyMemberHistory</t>
@@ -172,7 +172,7 @@
     <t>FRCDAAntecedentsFamiliaux.text</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-family-member-history-document</t>
+    <t>https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-family-member-history-document|0.1.0</t>
   </si>
   <si>
     <t>FRFamilyMemberHistoryDocument</t>

--- a/main/ig/FRFamilyMemberHistoryLMCDAFHIR.xlsx
+++ b/main/ig/FRFamilyMemberHistoryLMCDAFHIR.xlsx
@@ -9,12 +9,13 @@
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
     <sheet name="Mapping Table 0" r:id="rId4" sheetId="2"/>
     <sheet name="Mapping Table 1" r:id="rId5" sheetId="3"/>
+    <sheet name="Mapping Table 2" r:id="rId6" sheetId="4"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="68">
   <si>
     <t>Property</t>
   </si>
@@ -37,6 +38,9 @@
     <t>Name</t>
   </si>
   <si>
+    <t>FRFamilyMemberHistoryLMCDAFHIR</t>
+  </si>
+  <si>
     <t>Title</t>
   </si>
   <si>
@@ -52,10 +56,13 @@
     <t>Experimental</t>
   </si>
   <si>
+    <t>false</t>
+  </si>
+  <si>
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-20T08:45:34+00:00</t>
+    <t>2026-08-31T15:12:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -100,7 +107,7 @@
     <t>Target</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/fr-lm-family-member-history|0.1.0</t>
+    <t>https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/FRLMFamilyMemberHistory|0.1.0</t>
   </si>
   <si>
     <t/>
@@ -115,94 +122,103 @@
     <t>equivalent</t>
   </si>
   <si>
+    <t>Organizer</t>
+  </si>
+  <si>
     <t>FRCDAAntecedentsFamiliaux</t>
   </si>
   <si>
     <t>FRLMFamilyMemberHistory.header.status</t>
   </si>
   <si>
-    <t>FRCDAAntecedentsFamiliaux.statusCode</t>
+    <t>Organizer.statusCode</t>
   </si>
   <si>
     <t>FRLMFamilyMemberHistory.relatedPerson</t>
   </si>
   <si>
-    <t>FRCDAAntecedentsFamiliaux.subject.relatedSubject</t>
+    <t>Organizer.subject</t>
   </si>
   <si>
     <t>FRLMFamilyMemberHistory.condition</t>
   </si>
   <si>
-    <t>FRCDAAntecedentsFamiliaux.component:frAntecedentFamilialObserve</t>
+    <t>Organizer.component.observation</t>
+  </si>
+  <si>
+    <t>FRLMFamilyMemberHistory.note</t>
+  </si>
+  <si>
+    <t>related-to</t>
+  </si>
+  <si>
+    <t>Organizer.sdtcText</t>
+  </si>
+  <si>
+    <t>https://interop.esante.gouv.fr/ig/cda/document-core/StructureDefinition/fr-cda-antecedent-familial-observe|0.1.0</t>
   </si>
   <si>
     <t>FRLMFamilyMemberHistory.condition.code</t>
   </si>
   <si>
-    <t>FRCDAAntecedentsFamiliaux.component:frAntecedentFamilialObserve.code</t>
+    <t>Observation.code</t>
   </si>
   <si>
     <t>FRLMFamilyMemberHistory.condition.outcome</t>
   </si>
   <si>
-    <t>FRCDAAntecedentsFamiliaux.component:frAntecedentFamilialObserve.value</t>
+    <t>Observation.value</t>
   </si>
   <si>
     <t>FRLMFamilyMemberHistory.condition.contributedToDeath</t>
   </si>
   <si>
-    <t>related-to</t>
-  </si>
-  <si>
     <t>FRLMFamilyMemberHistory.condition.onset[x]</t>
   </si>
   <si>
-    <t>FRCDAAntecedentsFamiliaux.component:frAntecedentFamilialObserve.effectiveTime</t>
+    <t>Observation.effectiveTime</t>
   </si>
   <si>
     <t>FRLMFamilyMemberHistory.condition.bodySite</t>
   </si>
   <si>
-    <t>FRCDAAntecedentsFamiliaux.component:frAntecedentFamilialObserve.targetSiteCode</t>
-  </si>
-  <si>
-    <t>FRLMFamilyMemberHistory.note</t>
-  </si>
-  <si>
-    <t>FRCDAAntecedentsFamiliaux.text</t>
+    <t>Observation.targetSiteCode</t>
   </si>
   <si>
     <t>https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-family-member-history-document|0.1.0</t>
   </si>
   <si>
+    <t>FamilyMemberHistory</t>
+  </si>
+  <si>
     <t>FRFamilyMemberHistoryDocument</t>
   </si>
   <si>
-    <t>FRFamilyMemberHistoryDocument.status</t>
-  </si>
-  <si>
-    <t>FRFamilyMemberHistoryDocument.relationship</t>
-  </si>
-  <si>
-    <t>FRFamilyMemberHistoryDocument.condition</t>
-  </si>
-  <si>
-    <t>FRFamilyMemberHistoryDocument.condition.code</t>
-  </si>
-  <si>
-    <t>FRFamilyMemberHistoryDocument.condition.outcome</t>
-  </si>
-  <si>
-    <t>FRFamilyMemberHistoryDocument.condition.contributedToDeath</t>
-  </si>
-  <si>
-    <t>FRFamilyMemberHistoryDocument.condition.onset[x]</t>
-  </si>
-  <si>
-    <t>FRFamilyMemberHistoryDocument.condition.extension:FRFamilyMemberHistoryBodySiteExtension</t>
-  </si>
-  <si>
-    <t>FRFamilyMemberHistoryDocument.note</t>
+    <t>FamilyMemberHistory.status</t>
+  </si>
+  <si>
+    <t>FamilyMemberHistory.relationship</t>
+  </si>
+  <si>
+    <t>FamilyMemberHistory.condition</t>
+  </si>
+  <si>
+    <t>FamilyMemberHistory.condition.code</t>
+  </si>
+  <si>
+    <t>FamilyMemberHistory.condition.outcome</t>
+  </si>
+  <si>
+    <t>FamilyMemberHistory.condition.contributedToDeath</t>
+  </si>
+  <si>
+    <t>FamilyMemberHistory.condition.onset[x]</t>
+  </si>
+  <si>
+    <t>FamilyMemberHistory.condition.extension:bodySite</t>
+  </si>
+  <si>
+    <t>FamilyMemberHistory.note</t>
   </si>
 </sst>
 </file>
@@ -371,79 +387,83 @@
       <c r="A4" t="s" s="2">
         <v>6</v>
       </c>
-      <c r="B4" s="2"/>
+      <c r="B4" t="s" s="2">
+        <v>7</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>11</v>
-      </c>
-      <c r="B7" s="2"/>
+        <v>12</v>
+      </c>
+      <c r="B7" t="s" s="2">
+        <v>13</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B13" s="2"/>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B14" s="2"/>
     </row>
@@ -454,172 +474,109 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C1" t="s" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D1" t="s" s="1">
+        <v>29</v>
+      </c>
+      <c r="E1" t="s" s="1">
         <v>27</v>
-      </c>
-      <c r="E1" t="s" s="1">
-        <v>25</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C2" t="s" s="2">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D2" t="s" s="2">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E2" t="s" s="2">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D3" t="s" s="2">
-        <v>33</v>
-      </c>
-      <c r="E3" s="2"/>
+        <v>35</v>
+      </c>
+      <c r="E3" t="s" s="2">
+        <v>36</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D4" t="s" s="2">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="E4" s="2"/>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D5" t="s" s="2">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="E5" s="2"/>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D6" t="s" s="2">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="E6" s="2"/>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" t="s" s="2">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="D7" t="s" s="2">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="E7" s="2"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="s" s="2">
-        <v>42</v>
-      </c>
-      <c r="B8" s="2"/>
-      <c r="C8" t="s" s="2">
-        <v>32</v>
-      </c>
-      <c r="D8" t="s" s="2">
-        <v>43</v>
-      </c>
-      <c r="E8" s="2"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="s" s="2">
-        <v>44</v>
-      </c>
-      <c r="B9" s="2"/>
-      <c r="C9" t="s" s="2">
-        <v>45</v>
-      </c>
-      <c r="D9" t="s" s="2">
-        <v>43</v>
-      </c>
-      <c r="E9" s="2"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="s" s="2">
-        <v>46</v>
-      </c>
-      <c r="B10" s="2"/>
-      <c r="C10" t="s" s="2">
-        <v>32</v>
-      </c>
-      <c r="D10" t="s" s="2">
-        <v>47</v>
-      </c>
-      <c r="E10" s="2"/>
-    </row>
-    <row r="11">
-      <c r="A11" t="s" s="2">
-        <v>48</v>
-      </c>
-      <c r="B11" s="2"/>
-      <c r="C11" t="s" s="2">
-        <v>32</v>
-      </c>
-      <c r="D11" t="s" s="2">
-        <v>49</v>
-      </c>
-      <c r="E11" s="2"/>
-    </row>
-    <row r="12">
-      <c r="A12" t="s" s="2">
-        <v>50</v>
-      </c>
-      <c r="B12" s="2"/>
-      <c r="C12" t="s" s="2">
-        <v>45</v>
-      </c>
-      <c r="D12" t="s" s="2">
-        <v>51</v>
-      </c>
-      <c r="E12" s="2"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
@@ -628,170 +585,281 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:E7"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="1">
+        <v>26</v>
+      </c>
+      <c r="B1" t="s" s="1">
+        <v>27</v>
+      </c>
+      <c r="C1" t="s" s="1">
+        <v>28</v>
+      </c>
+      <c r="D1" t="s" s="1">
+        <v>29</v>
+      </c>
+      <c r="E1" t="s" s="1">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="B2" t="s" s="2">
+        <v>31</v>
+      </c>
+      <c r="C2" t="s" s="2">
+        <v>31</v>
+      </c>
+      <c r="D2" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="E2" t="s" s="2">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B3" s="2"/>
+      <c r="C3" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="D3" t="s" s="2">
+        <v>48</v>
+      </c>
+      <c r="E3" s="2"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="2">
+        <v>49</v>
+      </c>
+      <c r="B4" s="2"/>
+      <c r="C4" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="D4" t="s" s="2">
+        <v>50</v>
+      </c>
+      <c r="E4" s="2"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="2">
+        <v>51</v>
+      </c>
+      <c r="B5" s="2"/>
+      <c r="C5" t="s" s="2">
+        <v>44</v>
+      </c>
+      <c r="D5" t="s" s="2">
+        <v>50</v>
+      </c>
+      <c r="E5" s="2"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="2">
+        <v>52</v>
+      </c>
+      <c r="B6" s="2"/>
+      <c r="C6" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="D6" t="s" s="2">
+        <v>53</v>
+      </c>
+      <c r="E6" s="2"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="2">
+        <v>54</v>
+      </c>
+      <c r="B7" s="2"/>
+      <c r="C7" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="D7" t="s" s="2">
+        <v>55</v>
+      </c>
+      <c r="E7" s="2"/>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1:E12"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C1" t="s" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D1" t="s" s="1">
+        <v>29</v>
+      </c>
+      <c r="E1" t="s" s="1">
         <v>27</v>
-      </c>
-      <c r="E1" t="s" s="1">
-        <v>25</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C2" t="s" s="2">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D2" t="s" s="2">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="E2" t="s" s="2">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D3" t="s" s="2">
-        <v>53</v>
-      </c>
-      <c r="E3" s="2"/>
+        <v>57</v>
+      </c>
+      <c r="E3" t="s" s="2">
+        <v>58</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D4" t="s" s="2">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="E4" s="2"/>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" t="s" s="2">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D5" t="s" s="2">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="E5" s="2"/>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D6" t="s" s="2">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="E6" s="2"/>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D7" t="s" s="2">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="E7" s="2"/>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D8" t="s" s="2">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="E8" s="2"/>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="B9" s="2"/>
       <c r="C9" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D9" t="s" s="2">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="E9" s="2"/>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="B10" s="2"/>
       <c r="C10" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D10" t="s" s="2">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="E10" s="2"/>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="B11" s="2"/>
       <c r="C11" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D11" t="s" s="2">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="E11" s="2"/>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="B12" s="2"/>
       <c r="C12" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D12" t="s" s="2">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="E12" s="2"/>
     </row>

--- a/main/ig/FRFamilyMemberHistoryLMCDAFHIR.xlsx
+++ b/main/ig/FRFamilyMemberHistoryLMCDAFHIR.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T15:12:23+00:00</t>
+    <t>2026-09-04T14:19:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
